--- a/sample-datasheet.xlsx
+++ b/sample-datasheet.xlsx
@@ -13,19 +13,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Picture</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Dimension</t>
-  </si>
-  <si>
-    <t>Specification</t>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>IMAGE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>DIAGRAM</t>
+  </si>
+  <si>
+    <t>SPECS</t>
   </si>
   <si>
     <t>Azoogi LED Downlight 10W</t>
